--- a/final_data_pipeline/output/322130_kraft_elec.xlsx
+++ b/final_data_pipeline/output/322130_kraft_elec.xlsx
@@ -1020,7 +1020,7 @@
         <v>73</v>
       </c>
       <c r="K8">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="L8">
         <v>8000</v>
@@ -1067,7 +1067,7 @@
         <v>72</v>
       </c>
       <c r="K9">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="L9">
         <v>8000</v>
@@ -1082,10 +1082,10 @@
         <v>1419151.02748878</v>
       </c>
       <c r="R9">
-        <v>2.983181818181818</v>
+        <v>3.135414186445925</v>
       </c>
       <c r="S9">
-        <v>3.590555555555556</v>
+        <v>3.817068050129936</v>
       </c>
       <c r="T9">
         <v>177.3938784360975</v>
@@ -1126,7 +1126,7 @@
         <v>70</v>
       </c>
       <c r="K10">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="L10">
         <v>8000</v>
@@ -1147,10 +1147,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R10">
-        <v>1.800714285714286</v>
+        <v>1.847705673092716</v>
       </c>
       <c r="S10">
-        <v>1.963947368421052</v>
+        <v>2.020749367497032</v>
       </c>
       <c r="T10">
         <v>285.7998259898003</v>
@@ -1356,7 +1356,7 @@
         <v>70</v>
       </c>
       <c r="K14">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="L14">
         <v>8000</v>
@@ -1377,10 +1377,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R14">
-        <v>1.800714285714286</v>
+        <v>1.92665172779809</v>
       </c>
       <c r="S14">
-        <v>1.963947368421052</v>
+        <v>2.116885095206829</v>
       </c>
       <c r="T14">
         <v>185.794286928455</v>
@@ -1415,7 +1415,7 @@
         <v>72</v>
       </c>
       <c r="K15">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="L15">
         <v>8000</v>
@@ -1430,10 +1430,10 @@
         <v>922569.3272656928</v>
       </c>
       <c r="R15">
-        <v>2.983181818181818</v>
+        <v>3.408530896850205</v>
       </c>
       <c r="S15">
-        <v>3.590555555555556</v>
+        <v>4.236746585735966</v>
       </c>
       <c r="T15">
         <v>115.3211659082116</v>
@@ -1468,7 +1468,7 @@
         <v>73</v>
       </c>
       <c r="K16">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="L16">
         <v>8000</v>
@@ -2016,7 +2016,7 @@
         <v>70</v>
       </c>
       <c r="K26">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="L26">
         <v>8000</v>
@@ -2037,10 +2037,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R26">
-        <v>1.800714285714286</v>
+        <v>1.847705673092716</v>
       </c>
       <c r="S26">
-        <v>1.963947368421052</v>
+        <v>2.020749367497032</v>
       </c>
       <c r="T26">
         <v>105.4801463758995</v>
@@ -2075,7 +2075,7 @@
         <v>72</v>
       </c>
       <c r="K27">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="L27">
         <v>8000</v>
@@ -2090,10 +2090,10 @@
         <v>523766.092546071</v>
       </c>
       <c r="R27">
-        <v>2.983181818181818</v>
+        <v>3.135414186445925</v>
       </c>
       <c r="S27">
-        <v>3.590555555555556</v>
+        <v>3.817068050129936</v>
       </c>
       <c r="T27">
         <v>65.47076156825888</v>
@@ -2128,7 +2128,7 @@
         <v>73</v>
       </c>
       <c r="K28">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="L28">
         <v>8000</v>
@@ -2882,7 +2882,7 @@
         <v>72</v>
       </c>
       <c r="K42">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="L42">
         <v>8000</v>
@@ -2897,10 +2897,10 @@
         <v>753812.5397761788</v>
       </c>
       <c r="R42">
-        <v>2.983181818181818</v>
+        <v>2.455497817501559</v>
       </c>
       <c r="S42">
-        <v>3.590555555555556</v>
+        <v>2.843656807626497</v>
       </c>
       <c r="T42">
         <v>94.22656747202235</v>
@@ -2935,7 +2935,7 @@
         <v>73</v>
       </c>
       <c r="K43">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="L43">
         <v>8000</v>
@@ -2988,7 +2988,7 @@
         <v>70</v>
       </c>
       <c r="K44">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="L44">
         <v>8000</v>
@@ -3009,10 +3009,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R44">
-        <v>1.800714285714286</v>
+        <v>1.618523362263702</v>
       </c>
       <c r="S44">
-        <v>1.963947368421052</v>
+        <v>1.746638928617865</v>
       </c>
       <c r="T44">
         <v>151.8087141706027</v>
@@ -3047,7 +3047,7 @@
         <v>73</v>
       </c>
       <c r="K45">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="L45">
         <v>8000</v>
@@ -3100,7 +3100,7 @@
         <v>70</v>
       </c>
       <c r="K46">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="L46">
         <v>8000</v>
@@ -3121,10 +3121,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R46">
-        <v>1.800714285714286</v>
+        <v>1.865062221714807</v>
       </c>
       <c r="S46">
-        <v>1.963947368421052</v>
+        <v>2.041808739708676</v>
       </c>
       <c r="T46">
         <v>198.1001206187846</v>
@@ -3159,7 +3159,7 @@
         <v>72</v>
       </c>
       <c r="K47">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="L47">
         <v>8000</v>
@@ -3174,10 +3174,10 @@
         <v>983674.4607809267</v>
       </c>
       <c r="R47">
-        <v>2.983181818181818</v>
+        <v>3.193530074341067</v>
       </c>
       <c r="S47">
-        <v>3.590555555555556</v>
+        <v>3.904917482517481</v>
       </c>
       <c r="T47">
         <v>122.9593075976158</v>
@@ -3377,7 +3377,7 @@
         <v>72</v>
       </c>
       <c r="K51">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="L51">
         <v>8000</v>
@@ -3392,10 +3392,10 @@
         <v>140192.2543524546</v>
       </c>
       <c r="R51">
-        <v>2.983181818181818</v>
+        <v>3.15624931769735</v>
       </c>
       <c r="S51">
-        <v>3.590555555555556</v>
+        <v>3.848474349579903</v>
       </c>
       <c r="T51">
         <v>17.52403179405683</v>
@@ -3430,7 +3430,7 @@
         <v>73</v>
       </c>
       <c r="K52">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="L52">
         <v>8000</v>
@@ -3483,7 +3483,7 @@
         <v>70</v>
       </c>
       <c r="K53">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="L53">
         <v>8000</v>
@@ -3504,10 +3504,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R53">
-        <v>1.800714285714286</v>
+        <v>1.853964204859962</v>
       </c>
       <c r="S53">
-        <v>1.963947368421052</v>
+        <v>2.02833814451736</v>
       </c>
       <c r="T53">
         <v>28.23302180173783</v>
@@ -3542,7 +3542,7 @@
         <v>73</v>
       </c>
       <c r="K54">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="L54">
         <v>8000</v>
@@ -3589,7 +3589,7 @@
         <v>72</v>
       </c>
       <c r="K55">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="L55">
         <v>8000</v>
@@ -3604,10 +3604,10 @@
         <v>499496.9096867541</v>
       </c>
       <c r="R55">
-        <v>2.983181818181818</v>
+        <v>2.455497817501559</v>
       </c>
       <c r="S55">
-        <v>3.590555555555556</v>
+        <v>2.843656807626497</v>
       </c>
       <c r="T55">
         <v>62.43711371084427</v>
@@ -3648,7 +3648,7 @@
         <v>70</v>
       </c>
       <c r="K56">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="L56">
         <v>8000</v>
@@ -3669,10 +3669,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R56">
-        <v>1.800714285714286</v>
+        <v>1.618523362263702</v>
       </c>
       <c r="S56">
-        <v>1.963947368421052</v>
+        <v>1.746638928617865</v>
       </c>
       <c r="T56">
         <v>100.5926269338137</v>
@@ -3872,7 +3872,7 @@
         <v>73</v>
       </c>
       <c r="K60">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="L60">
         <v>8000</v>
@@ -3925,7 +3925,7 @@
         <v>70</v>
       </c>
       <c r="K61">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="L61">
         <v>8000</v>
@@ -3946,10 +3946,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R61">
-        <v>1.800714285714286</v>
+        <v>1.853964204859962</v>
       </c>
       <c r="S61">
-        <v>1.963947368421052</v>
+        <v>2.02833814451736</v>
       </c>
       <c r="T61">
         <v>51.21183095391873</v>
@@ -3984,7 +3984,7 @@
         <v>72</v>
       </c>
       <c r="K62">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="L62">
         <v>8000</v>
@@ -3999,10 +3999,10 @@
         <v>254294.4953382484</v>
       </c>
       <c r="R62">
-        <v>2.983181818181818</v>
+        <v>3.15624931769735</v>
       </c>
       <c r="S62">
-        <v>3.590555555555556</v>
+        <v>3.848474349579903</v>
       </c>
       <c r="T62">
         <v>31.78681191728105</v>
@@ -4202,7 +4202,7 @@
         <v>72</v>
       </c>
       <c r="K66">
-        <v>10</v>
+        <v>19.36574074074073</v>
       </c>
       <c r="L66">
         <v>8000</v>
@@ -4217,10 +4217,10 @@
         <v>379499.9015699624</v>
       </c>
       <c r="R66">
-        <v>2.983181818181818</v>
+        <v>3.595434716445165</v>
       </c>
       <c r="S66">
-        <v>3.590555555555556</v>
+        <v>4.534260101338181</v>
       </c>
       <c r="T66">
         <v>47.4374876962453</v>
@@ -4261,7 +4261,7 @@
         <v>70</v>
       </c>
       <c r="K67">
-        <v>10</v>
+        <v>19.36574074074073</v>
       </c>
       <c r="L67">
         <v>8000</v>
@@ -4282,10 +4282,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R67">
-        <v>1.800714285714286</v>
+        <v>1.977063465169192</v>
       </c>
       <c r="S67">
-        <v>1.963947368421052</v>
+        <v>2.178742498783586</v>
       </c>
       <c r="T67">
         <v>76.42668308796266</v>
@@ -4320,7 +4320,7 @@
         <v>73</v>
       </c>
       <c r="K68">
-        <v>10</v>
+        <v>19.36574074074073</v>
       </c>
       <c r="L68">
         <v>8000</v>
@@ -4367,7 +4367,7 @@
         <v>72</v>
       </c>
       <c r="K69">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="L69">
         <v>8000</v>
@@ -4382,10 +4382,10 @@
         <v>315991.6826555474</v>
       </c>
       <c r="R69">
-        <v>2.983181818181818</v>
+        <v>3.193530074341067</v>
       </c>
       <c r="S69">
-        <v>3.590555555555556</v>
+        <v>3.904917482517481</v>
       </c>
       <c r="T69">
         <v>39.49896033194342</v>
@@ -4426,7 +4426,7 @@
         <v>70</v>
       </c>
       <c r="K70">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="L70">
         <v>8000</v>
@@ -4447,10 +4447,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R70">
-        <v>1.800714285714286</v>
+        <v>1.865062221714807</v>
       </c>
       <c r="S70">
-        <v>1.963947368421052</v>
+        <v>2.041808739708676</v>
       </c>
       <c r="T70">
         <v>63.63689710811531</v>
@@ -4485,7 +4485,7 @@
         <v>73</v>
       </c>
       <c r="K71">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="L71">
         <v>8000</v>
@@ -4697,7 +4697,7 @@
         <v>73</v>
       </c>
       <c r="K75">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="L75">
         <v>8000</v>
@@ -4750,7 +4750,7 @@
         <v>70</v>
       </c>
       <c r="K76">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="L76">
         <v>8000</v>
@@ -4771,10 +4771,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R76">
-        <v>1.800714285714286</v>
+        <v>1.983015294974508</v>
       </c>
       <c r="S76">
-        <v>1.963947368421052</v>
+        <v>2.18606997558991</v>
       </c>
       <c r="T76">
         <v>171.5330582737022</v>
@@ -4809,7 +4809,7 @@
         <v>72</v>
       </c>
       <c r="K77">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="L77">
         <v>8000</v>
@@ -4824,10 +4824,10 @@
         <v>851754.5980105142</v>
       </c>
       <c r="R77">
-        <v>2.983181818181818</v>
+        <v>3.618192955589586</v>
       </c>
       <c r="S77">
-        <v>3.590555555555556</v>
+        <v>4.571080550098231</v>
       </c>
       <c r="T77">
         <v>106.4693247513143</v>
@@ -5687,7 +5687,7 @@
         <v>73</v>
       </c>
       <c r="K93">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="L93">
         <v>8000</v>
@@ -5734,7 +5734,7 @@
         <v>72</v>
       </c>
       <c r="K94">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="L94">
         <v>8000</v>
@@ -5749,10 +5749,10 @@
         <v>477931.0004827667</v>
       </c>
       <c r="R94">
-        <v>2.983181818181818</v>
+        <v>3.15624931769735</v>
       </c>
       <c r="S94">
-        <v>3.590555555555556</v>
+        <v>3.848474349579903</v>
       </c>
       <c r="T94">
         <v>59.74137506034583</v>
@@ -5793,7 +5793,7 @@
         <v>70</v>
       </c>
       <c r="K95">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="L95">
         <v>8000</v>
@@ -5814,10 +5814,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R95">
-        <v>1.800714285714286</v>
+        <v>1.853964204859962</v>
       </c>
       <c r="S95">
-        <v>1.963947368421052</v>
+        <v>2.02833814451736</v>
       </c>
       <c r="T95">
         <v>96.24951405969072</v>
@@ -6017,7 +6017,7 @@
         <v>72</v>
       </c>
       <c r="K99">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="L99">
         <v>8000</v>
@@ -6032,10 +6032,10 @@
         <v>1937556.489427135</v>
       </c>
       <c r="R99">
-        <v>2.983181818181818</v>
+        <v>2.455497817501559</v>
       </c>
       <c r="S99">
-        <v>3.590555555555556</v>
+        <v>2.843656807626497</v>
       </c>
       <c r="T99">
         <v>242.1945611783918</v>
@@ -6076,7 +6076,7 @@
         <v>70</v>
       </c>
       <c r="K100">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="L100">
         <v>8000</v>
@@ -6097,10 +6097,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R100">
-        <v>1.800714285714286</v>
+        <v>1.618523362263702</v>
       </c>
       <c r="S100">
-        <v>1.963947368421052</v>
+        <v>1.746638928617865</v>
       </c>
       <c r="T100">
         <v>390.200406297533</v>
@@ -6135,7 +6135,7 @@
         <v>73</v>
       </c>
       <c r="K101">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="L101">
         <v>8000</v>
@@ -6347,7 +6347,7 @@
         <v>72</v>
       </c>
       <c r="K105">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="L105">
         <v>8000</v>
@@ -6362,10 +6362,10 @@
         <v>2443084.823108844</v>
       </c>
       <c r="R105">
-        <v>2.983181818181818</v>
+        <v>2.756919486581097</v>
       </c>
       <c r="S105">
-        <v>3.590555555555556</v>
+        <v>3.263225806451613</v>
       </c>
       <c r="T105">
         <v>305.3856028886055</v>
@@ -6406,7 +6406,7 @@
         <v>70</v>
       </c>
       <c r="K106">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="L106">
         <v>8000</v>
@@ -6427,10 +6427,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R106">
-        <v>1.800714285714286</v>
+        <v>1.726493341788205</v>
       </c>
       <c r="S106">
-        <v>1.963947368421052</v>
+        <v>1.874863921842289</v>
       </c>
       <c r="T106">
         <v>492.0076889620191</v>
@@ -6465,7 +6465,7 @@
         <v>73</v>
       </c>
       <c r="K107">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="L107">
         <v>8000</v>
